--- a/medias_mensuales.xlsx
+++ b/medias_mensuales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,6 +578,73 @@
       </c>
       <c r="S2" t="n">
         <v>10.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="P3" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>694</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
